--- a/tracker/Filter_Order_Log.xlsx
+++ b/tracker/Filter_Order_Log.xlsx
@@ -66,14 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -440,17 +439,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,7 +464,11 @@
           <t>Job number</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2250823</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -467,7 +476,11 @@
           <t>Project name</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Austin Stone</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -480,192 +493,380 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>PO number</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
+          <t>Airco PM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Airco PM</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
           <t>Ordered by</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Angel Leon</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Order date</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Filter set (1/2/3/Attic)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Vendor SO #</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Our PO #</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>MERV</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Order total price</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Unit price</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Line total</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Units it went to</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Order date</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Filter set (1/2/3/Attic)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Filter order #</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Order total price</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Qty ordered</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Units it went to</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tex Air Austin</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>766028</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>98.23999999999999</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>20x25x4</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="K8" s="4">
+        <f>I8*J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Customer pickup</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Urgent, units unknown at time of order. Email request was 9/25, receipt dated 9/22 - confirm date.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>20x25x4</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tex Air Austin</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>766028</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="2" t="n"/>
+      <c r="G9" s="4" t="n"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Urgent, units unknown at time of order</t>
-        </is>
-      </c>
+          <t>20x20x4</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="K9" s="4">
+        <f>I9*J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>20x20x4</t>
-        </is>
-      </c>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tex Air Austin</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>770738</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n"/>
       <c r="F10" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" s="2" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>368.44</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>20x25x4</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="K10" s="4">
+        <f>I10*J10</f>
+        <v/>
+      </c>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Delivered 2026-10-09</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Units unknown at time of order.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>20x25x4</t>
-        </is>
-      </c>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tex Air Austin</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>770738</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n"/>
       <c r="F11" t="n">
-        <v>16</v>
-      </c>
-      <c r="G11" s="2" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="G11" s="4" t="n"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Units unknown at time of order</t>
-        </is>
-      </c>
+          <t>20x25x2</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>24</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="K11" s="4">
+        <f>I11*J11</f>
+        <v/>
+      </c>
+      <c r="L11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>20x25x2</t>
-        </is>
-      </c>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tex Air Austin</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>770738</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
       <c r="F12" t="n">
-        <v>24</v>
-      </c>
-      <c r="G12" s="2" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>20x20x4</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="K12" s="4">
+        <f>I12*J12</f>
+        <v/>
+      </c>
+      <c r="L12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>20x20x4</t>
-        </is>
-      </c>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tex Air Austin</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>770738</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" t="inlineStr">
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>20x20x2</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="I13" t="n">
         <v>12</v>
       </c>
-      <c r="G14" s="2" t="n"/>
+      <c r="J13" s="4" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="K13" s="4">
+        <f>I13*J13</f>
+        <v/>
+      </c>
+      <c r="L13" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -722,7 +923,7 @@
         </is>
       </c>
       <c r="B2">
-        <f>SUMIF('Order Log'!$E$9:$E$14,A2,'Order Log'!$F$9:$F$14)</f>
+        <f>SUMIF('Order Log'!$H$8:$H$13,A2,'Order Log'!$I$8:$I$13)</f>
         <v/>
       </c>
       <c r="C2" t="n">
@@ -743,7 +944,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>SUMIF('Order Log'!$E$9:$E$14,A3,'Order Log'!$F$9:$F$14)</f>
+        <f>SUMIF('Order Log'!$H$8:$H$13,A3,'Order Log'!$I$8:$I$13)</f>
         <v/>
       </c>
       <c r="C3" t="n">
@@ -764,7 +965,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>SUMIF('Order Log'!$E$9:$E$14,A4,'Order Log'!$F$9:$F$14)</f>
+        <f>SUMIF('Order Log'!$H$8:$H$13,A4,'Order Log'!$I$8:$I$13)</f>
         <v/>
       </c>
       <c r="C4" t="n">
@@ -785,7 +986,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>SUMIF('Order Log'!$E$9:$E$14,A5,'Order Log'!$F$9:$F$14)</f>
+        <f>SUMIF('Order Log'!$H$8:$H$13,A5,'Order Log'!$I$8:$I$13)</f>
         <v/>
       </c>
       <c r="C5" t="n">
@@ -806,7 +1007,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>SUMIF('Order Log'!$E$9:$E$14,A6,'Order Log'!$F$9:$F$14)</f>
+        <f>SUMIF('Order Log'!$H$8:$H$13,A6,'Order Log'!$I$8:$I$13)</f>
         <v/>
       </c>
       <c r="C6" t="n">
@@ -827,7 +1028,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>SUMIF('Order Log'!$E$9:$E$14,A7,'Order Log'!$F$9:$F$14)</f>
+        <f>SUMIF('Order Log'!$H$8:$H$13,A7,'Order Log'!$I$8:$I$13)</f>
         <v/>
       </c>
       <c r="C7" t="n">
@@ -848,7 +1049,7 @@
         </is>
       </c>
       <c r="B8">
-        <f>SUMIF('Order Log'!$E$9:$E$14,A8,'Order Log'!$F$9:$F$14)</f>
+        <f>SUMIF('Order Log'!$H$8:$H$13,A8,'Order Log'!$I$8:$I$13)</f>
         <v/>
       </c>
       <c r="C8" t="n">
@@ -869,7 +1070,7 @@
         </is>
       </c>
       <c r="B9">
-        <f>SUMIF('Order Log'!$E$9:$E$14,A9,'Order Log'!$F$9:$F$14)</f>
+        <f>SUMIF('Order Log'!$H$8:$H$13,A9,'Order Log'!$I$8:$I$13)</f>
         <v/>
       </c>
       <c r="C9" t="n">

--- a/tracker/Filter_Order_Log.xlsx
+++ b/tracker/Filter_Order_Log.xlsx
@@ -607,7 +607,11 @@
           <t>766028</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>380118</t>
+        </is>
+      </c>
       <c r="F8" t="n">
         <v>8</v>
       </c>
@@ -637,7 +641,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Urgent, units unknown at time of order. Email request was 9/25, receipt dated 9/22 - confirm date.</t>
+          <t>Urgent, units unknown at time of order.</t>
         </is>
       </c>
     </row>
@@ -662,7 +666,11 @@
           <t>766028</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>380118</t>
+        </is>
+      </c>
       <c r="F9" t="n">
         <v>8</v>
       </c>
@@ -705,7 +713,11 @@
           <t>770738</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>382244</t>
+        </is>
+      </c>
       <c r="F10" t="n">
         <v>8</v>
       </c>
@@ -760,7 +772,11 @@
           <t>770738</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>382244</t>
+        </is>
+      </c>
       <c r="F11" t="n">
         <v>8</v>
       </c>
@@ -803,7 +819,11 @@
           <t>770738</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>382244</t>
+        </is>
+      </c>
       <c r="F12" t="n">
         <v>8</v>
       </c>
@@ -846,7 +866,11 @@
           <t>770738</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>382244</t>
+        </is>
+      </c>
       <c r="F13" t="n">
         <v>8</v>
       </c>
